--- a/src/ex.xlsx
+++ b/src/ex.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,57 +446,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>supported_languages</t>
+          <t>developers</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>developers</t>
+          <t>publishers</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>publishers</t>
+          <t>price_overview</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>price_overview</t>
+          <t>categories</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>categories</t>
+          <t>genres</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>genres</t>
+          <t>recommendations</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>achievements</t>
+          <t>controller_support</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>release_date</t>
+          <t>dlc_count</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dlc</t>
+          <t>achievements_count</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>recommendations</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>controller_support</t>
+          <t>release_year</t>
         </is>
       </c>
     </row>
@@ -519,7 +514,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>EckGames</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -527,44 +522,35 @@
           <t>EckGames</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EckGames</t>
-        </is>
+      <c r="G2" t="n">
+        <v>899</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>PLN 899 899</t>
+          <t>Single-player, Steam Achievements, Steam Cloud, Steam Leaderboards, Family Sharing</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Single-player, Steam Achievements, Steam Cloud, Steam Leaderboards, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
           <t>Action, Adventure, Casual, Indie</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0 06/02/2018</t>
-        </is>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="3">
@@ -586,7 +572,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">English   , Korean, Traditional Chinese, Simplified Chinese     </t>
+          <t>Masangsoft</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -594,40 +580,35 @@
           <t>Masangsoft</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Masangsoft</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Multi-player, MMO, PvP, Online PvP, Co-op, Online Co-op, Steam Achievements, In-App Purchases</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Multi-player, MMO, PvP, Online PvP, Co-op, Online Co-op, Steam Achievements, In-App Purchases</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
           <t>Action, Adventure, Massively Multiplayer, RPG</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0 05/03/2019</t>
-        </is>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2019</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +634,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">English   , Traditional Chinese, Ukrainian     </t>
+          <t>Holomia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -661,40 +642,35 @@
           <t>Holomia</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Holomia</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Single-player, Multi-player, PvP, LAN PvP, Co-op, LAN Co-op, Cross-Platform Multiplayer</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Single-player, Multi-player, PvP, LAN PvP, Co-op, LAN Co-op, Cross-Platform Multiplayer</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
           <t>Action, Simulation</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0 20/07/2018</t>
-        </is>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="5">
@@ -716,7 +692,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>English, Japanese</t>
+          <t>Chilla's Art</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -724,44 +700,35 @@
           <t>Chilla's Art</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Chilla's Art</t>
-        </is>
+      <c r="G5" t="n">
+        <v>1349</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PLN 1349 1349</t>
+          <t>Single-player, Partial Controller Support, Family Sharing</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Single-player, Partial Controller Support, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
           <t>Adventure, Casual, Indie</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0 15/02/2018</t>
-        </is>
+      <c r="J5" t="n">
+        <v>163</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>163</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="6">
@@ -798,52 +765,43 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>CSM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CSM</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
           <t>W.T.B.</t>
         </is>
       </c>
+      <c r="G6" t="n">
+        <v>2299</v>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PLN 2299 2299</t>
+          <t>Single-player, Steam Achievements, Family Sharing</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Single-player, Steam Achievements, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
           <t>Casual, Indie</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0 22/01/2018</t>
-        </is>
-      </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="7">
@@ -865,7 +823,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">English        </t>
+          <t>Penumbra Games</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -873,44 +831,35 @@
           <t>Penumbra Games</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Penumbra Games</t>
-        </is>
+      <c r="G7" t="n">
+        <v>719</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PLN 719 719</t>
+          <t>Single-player, Steam Achievements, Steam Cloud, Family Sharing</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Single-player, Steam Achievements, Steam Cloud, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
           <t>Violent, Gore, Adventure, Indie</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0 26/01/2018</t>
-        </is>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="8">
@@ -932,7 +881,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>English, Spanish - Spain, Polish, French, Italian, German, Simplified Chinese, Japanese, Korean, Portuguese - Brazil, Turkish</t>
+          <t>Koksny.com</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -940,44 +889,35 @@
           <t>Koksny.com</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Koksny.com</t>
-        </is>
+      <c r="G8" t="n">
+        <v>5399</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PLN 5399 5399</t>
+          <t>Single-player, Steam Achievements, Steam Workshop, Partial Controller Support, Steam Cloud, Stats, Includes level editor, Family Sharing</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Single-player, Steam Achievements, Steam Workshop, Partial Controller Support, Steam Cloud, Stats, Includes level editor, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
           <t>Casual, Indie, Simulation</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0 31/03/2021</t>
-        </is>
+      <c r="J8" t="n">
+        <v>214</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="N8" t="n">
-        <v>214</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2021</v>
       </c>
     </row>
     <row r="9">
@@ -999,52 +939,43 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">English   , French, German, Spanish - Spain, Russian, Polish, Simplified Chinese     </t>
+          <t>Osaris Games</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Osaris Games</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
           <t>RockGame S.A.</t>
         </is>
       </c>
+      <c r="G9" t="n">
+        <v>6499</v>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PLN 6499 6499</t>
+          <t>Single-player, Multi-player, Co-op, Online Co-op, Steam Achievements, Steam Workshop, Family Sharing</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Single-player, Multi-player, Co-op, Online Co-op, Steam Achievements, Steam Workshop, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
           <t>Indie, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0 15/09/2022</t>
-        </is>
+      <c r="J9" t="n">
+        <v>192</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="N9" t="n">
-        <v>192</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2022</v>
       </c>
     </row>
     <row r="10">
@@ -1066,7 +997,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>English, Japanese, Korean, Simplified Chinese, Russian</t>
+          <t>narayana games UG</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1074,41 +1005,34 @@
           <t>narayana games UG</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>narayana games UG</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Single-player, Multi-player, Co-op, Online Co-op, LAN Co-op, Shared/Split Screen Co-op, Shared/Split Screen, Cross-Platform Multiplayer, Steam Achievements, Tracked Controller Support, VR Only, In-App Purchases, Stats, Steam Leaderboards, Includes level editor, Family Sharing</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Single-player, Multi-player, Co-op, Online Co-op, LAN Co-op, Shared/Split Screen Co-op, Shared/Split Screen, Cross-Platform Multiplayer, Steam Achievements, Tracked Controller Support, VR Only, In-App Purchases, Stats, Steam Leaderboards, Includes level editor, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
           <t>Casual, Indie, Sports</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1 To be announced</t>
-        </is>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1131,52 +1055,43 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">English        </t>
+          <t>Infogrames</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Infogrames</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
           <t>Atari</t>
         </is>
       </c>
+      <c r="G11" t="n">
+        <v>2899</v>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PLN 2899 2899</t>
+          <t>Single-player, Family Sharing</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Single-player, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
           <t>Adventure, RPG</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0 08/02/2018</t>
-        </is>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="12">
@@ -1205,52 +1120,43 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Infogrames</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Infogrames</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
           <t xml:space="preserve">Ziggurat </t>
         </is>
       </c>
+      <c r="G12" t="n">
+        <v>1799</v>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PLN 1799 539</t>
+          <t>Single-player, Multi-player, PvP, Shared/Split Screen PvP, Co-op, Remote Play Together, Family Sharing</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Single-player, Multi-player, PvP, Shared/Split Screen PvP, Co-op, Remote Play Together, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>0 08/02/2018</t>
-        </is>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="13">
@@ -1280,52 +1186,43 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">English        </t>
+          <t>Infogrames</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Infogrames</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
           <t>Ziggurat</t>
         </is>
       </c>
+      <c r="G13" t="n">
+        <v>2549</v>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PLN 2549 2549</t>
+          <t>Single-player, Family Sharing</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Single-player, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
           <t>Action, Adventure</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>0 08/02/2018</t>
-        </is>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="14">
@@ -1359,52 +1256,43 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">English        </t>
+          <t>Infogrames</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Infogrames</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
           <t>Ziggurat</t>
         </is>
       </c>
+      <c r="G14" t="n">
+        <v>2549</v>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PLN 2549 764</t>
+          <t>Single-player, Family Sharing</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Single-player, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
           <t>Action, Adventure, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>0 08/02/2018</t>
-        </is>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="15">
@@ -1437,52 +1325,43 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">English        </t>
+          <t>Infogrames</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Infogrames</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
           <t>Ziggurat</t>
         </is>
       </c>
+      <c r="G15" t="n">
+        <v>2549</v>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>PLN 2549 764</t>
+          <t>Single-player, Family Sharing</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Single-player, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
           <t>Action, Adventure</t>
         </is>
       </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>0 08/02/2018</t>
-        </is>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="16">
@@ -1523,52 +1402,43 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">English        </t>
+          <t>Infogrames</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Infogrames</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
           <t>Ziggurat</t>
         </is>
       </c>
+      <c r="G16" t="n">
+        <v>2549</v>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>PLN 2549 2549</t>
+          <t>Single-player, Family Sharing</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Single-player, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
           <t>Action, Adventure, RPG</t>
         </is>
       </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>0 08/02/2018</t>
-        </is>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="17">
@@ -1606,52 +1476,43 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">English        </t>
+          <t>Infogrames</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Infogrames</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
           <t>Atari</t>
         </is>
       </c>
+      <c r="G17" t="n">
+        <v>2549</v>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>PLN 2549 2549</t>
+          <t>Single-player, Family Sharing</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Single-player, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
           <t>Action, Strategy</t>
         </is>
       </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>0 08/02/2018</t>
-        </is>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="18">
@@ -1673,7 +1534,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">English        </t>
+          <t>VR Factory</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1681,44 +1542,35 @@
           <t>VR Factory</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VR Factory</t>
-        </is>
+      <c r="G18" t="n">
+        <v>3599</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>PLN 3599 3599</t>
+          <t>Single-player, Tracked Controller Support, VR Only, Family Sharing</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Single-player, Tracked Controller Support, VR Only, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
           <t>Action, Casual, Indie</t>
         </is>
       </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>0 26/01/2018</t>
-        </is>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="19">
@@ -1740,48 +1592,43 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">English   , Russian        </t>
+          <t>Foxoft</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Foxoft</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
           <t>AZAMATIKA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Single-player, Steam Achievements, Full controller support</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Single-player, Steam Achievements, Full controller support</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
           <t>Action, Adventure, Indie</t>
         </is>
       </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>0 20/02/2018</t>
-        </is>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="20">
@@ -1803,52 +1650,43 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Ethan Summers Alex Lamb Nainoa Faulkner-Jackson Lauren Hanf Ramsey Antrim-Kerr Kieran Wright Anne-Marie Napoli</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ethan Summers Alex Lamb Nainoa Faulkner-Jackson Lauren Hanf Ramsey Antrim-Kerr Kieran Wright Anne-Marie Napoli</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
           <t>Almost Human Media</t>
         </is>
       </c>
+      <c r="G20" t="n">
+        <v>8299</v>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>PLN 8299 8299</t>
+          <t>Single-player, VR Supported, Family Sharing</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Single-player, VR Supported, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
           <t>Casual, Indie</t>
         </is>
       </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>0 14/11/2024</t>
-        </is>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2024</v>
       </c>
     </row>
     <row r="21">
@@ -1870,52 +1708,43 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>English, German, Simplified Chinese</t>
+          <t>Dragon Slumber</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dragon Slumber</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
           <t>Iceberg Interactive</t>
         </is>
       </c>
+      <c r="G21" t="n">
+        <v>4599</v>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>PLN 4599 4599</t>
+          <t>Single-player, Steam Achievements, Steam Trading Cards, Steam Cloud, Family Sharing</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Single-player, Steam Achievements, Steam Trading Cards, Steam Cloud, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
           <t>Adventure, Casual, Indie, Simulation</t>
         </is>
       </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>0 27/02/2019</t>
-        </is>
+      <c r="J21" t="n">
+        <v>561</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="N21" t="n">
-        <v>561</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2019</v>
       </c>
     </row>
     <row r="22">
@@ -1937,7 +1766,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>English, Simplified Chinese, Traditional Chinese</t>
+          <t>Fish Chain Games</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1945,44 +1774,35 @@
           <t>Fish Chain Games</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Fish Chain Games</t>
-        </is>
+      <c r="G22" t="n">
+        <v>899</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>PLN 899 899</t>
+          <t>Single-player, Steam Achievements, Full controller support, Steam Cloud, Stats, Family Sharing</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Single-player, Steam Achievements, Full controller support, Steam Cloud, Stats, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
           <t>Casual, Indie</t>
         </is>
       </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>0 05/02/2018</t>
-        </is>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="23">
@@ -2004,7 +1824,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">English   , Simplified Chinese   , Traditional Chinese        </t>
+          <t>BD Studio Games</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2012,44 +1832,35 @@
           <t>BD Studio Games</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>BD Studio Games</t>
-        </is>
+      <c r="G23" t="n">
+        <v>1099</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>PLN 1099 1099</t>
+          <t>Single-player, Family Sharing</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Single-player, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
           <t>Action, Casual, Indie</t>
         </is>
       </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>0 31/01/2018</t>
-        </is>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="24">
@@ -2071,7 +1882,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">English        </t>
+          <t>Eternity Studios</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2079,44 +1890,35 @@
           <t>Eternity Studios</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Eternity Studios</t>
-        </is>
+      <c r="G24" t="n">
+        <v>1449</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PLN 1449 1449</t>
+          <t>Single-player, Steam Achievements, Family Sharing</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Single-player, Steam Achievements, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
           <t>Action, Adventure, Casual, Indie, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="K24" t="n">
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>0 28/01/2018</t>
-        </is>
       </c>
       <c r="M24" t="n">
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="25">
@@ -2138,7 +1940,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Simplified Chinese   , Traditional Chinese        </t>
+          <t>Flying Star Games</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2146,44 +1948,35 @@
           <t>Flying Star Games</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Flying Star Games</t>
-        </is>
+      <c r="G25" t="n">
+        <v>2199</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PLN 2199 2199</t>
+          <t>Single-player, Family Sharing</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Single-player, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
           <t>Adventure, RPG, Strategy</t>
         </is>
       </c>
-      <c r="K25" t="n">
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>0 02/02/2018</t>
-        </is>
-      </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="26">
@@ -2212,52 +2005,43 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>ARGames</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ARGames</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
           <t>Metal Fox</t>
         </is>
       </c>
+      <c r="G26" t="n">
+        <v>449</v>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PLN 449 449</t>
+          <t>Single-player, Steam Achievements, Family Sharing</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Single-player, Steam Achievements, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
           <t>Adventure, Indie</t>
         </is>
       </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>0 24/01/2018</t>
-        </is>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="27">
@@ -2279,52 +2063,43 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Iffy Labs</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Iffy Labs</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
           <t>hOSHI</t>
         </is>
       </c>
+      <c r="G27" t="n">
+        <v>2199</v>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>PLN 2199 2199</t>
+          <t>Multi-player, PvP, Online PvP, Shared/Split Screen PvP, Co-op, Online Co-op, Shared/Split Screen Co-op, Shared/Split Screen, Steam Achievements, Full controller support, Remote Play Together, Family Sharing</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Multi-player, PvP, Online PvP, Shared/Split Screen PvP, Co-op, Online Co-op, Shared/Split Screen Co-op, Shared/Split Screen, Steam Achievements, Full controller support, Remote Play Together, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
           <t>Action, Casual, Indie, Strategy</t>
         </is>
       </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>0 01/02/2019</t>
-        </is>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+        <v>2019</v>
       </c>
     </row>
     <row r="28">
@@ -2346,7 +2121,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Luke O'Connor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2354,44 +2129,35 @@
           <t>Luke O'Connor</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Luke O'Connor</t>
-        </is>
+      <c r="G28" t="n">
+        <v>2549</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>PLN 2549 2549</t>
+          <t>Single-player, Partial Controller Support, Family Sharing</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Single-player, Partial Controller Support, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
           <t>Action, Casual, Indie</t>
         </is>
       </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>0 02/05/2018</t>
-        </is>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="29">
@@ -2433,7 +2199,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>FurGoldGames</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2441,44 +2207,35 @@
           <t>FurGoldGames</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>FurGoldGames</t>
-        </is>
+      <c r="G29" t="n">
+        <v>359</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>PLN 359 359</t>
+          <t>Single-player, Steam Achievements, Steam Leaderboards, Family Sharing</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Single-player, Steam Achievements, Steam Leaderboards, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
           <t>Indie, Racing, Simulation</t>
         </is>
       </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>0 23/01/2018</t>
-        </is>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="30">
@@ -2500,7 +2257,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">English        </t>
+          <t>RewindApp</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2508,44 +2265,35 @@
           <t>RewindApp</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>RewindApp</t>
-        </is>
+      <c r="G30" t="n">
+        <v>800</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>PLN 800 800</t>
+          <t>Single-player, Family Sharing</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Single-player, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
           <t>Casual, Indie</t>
         </is>
       </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>0 07/02/2018</t>
-        </is>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="31">
@@ -2567,7 +2315,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Magnolia Art</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2575,40 +2323,35 @@
           <t>Magnolia Art</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Magnolia Art</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Single-player, Steam Achievements, Steam Cloud, Steam Leaderboards</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Single-player, Steam Achievements, Steam Cloud, Steam Leaderboards</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
           <t>Casual, Indie</t>
         </is>
       </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>0 07/03/2018</t>
-        </is>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="32">
@@ -2630,7 +2373,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>ocasocreations</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2638,44 +2381,35 @@
           <t>ocasocreations</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ocasocreations</t>
-        </is>
+      <c r="G32" t="n">
+        <v>3699</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>PLN 3699 3699</t>
+          <t>Single-player, Multi-player, PvP, Shared/Split Screen PvP, Shared/Split Screen, Steam Achievements, Partial Controller Support, Remote Play Together, Family Sharing</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Single-player, Multi-player, PvP, Shared/Split Screen PvP, Shared/Split Screen, Steam Achievements, Partial Controller Support, Remote Play Together, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
           <t>Indie</t>
         </is>
       </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>0 18/03/2019</t>
-        </is>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2019</v>
       </c>
     </row>
     <row r="33">
@@ -2705,7 +2439,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Sick Kreations</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2713,41 +2447,34 @@
           <t>Sick Kreations</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Sick Kreations</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Multi-player, PvP, Online PvP, Family Sharing</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Multi-player, PvP, Online PvP, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
           <t>Action, Indie</t>
         </is>
       </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>1 Coming soon</t>
-        </is>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -2776,7 +2503,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">English        </t>
+          <t>Ripknot Systems</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2784,44 +2511,35 @@
           <t>Ripknot Systems</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Ripknot Systems</t>
-        </is>
+      <c r="G34" t="n">
+        <v>6399</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>PLN 6399 6399</t>
+          <t>Single-player, Steam Achievements, Family Sharing</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Single-player, Steam Achievements, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
           <t>Casual, Indie, Simulation, Strategy</t>
         </is>
       </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>0 23/01/2018</t>
-        </is>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>5000</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="35">
@@ -2843,7 +2561,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>AnderShi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2851,44 +2569,35 @@
           <t>AnderShi</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>AnderShi</t>
-        </is>
+      <c r="G35" t="n">
+        <v>359</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>PLN 359 359</t>
+          <t>Single-player, Family Sharing</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Single-player, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
           <t>Adventure, Indie, Simulation</t>
         </is>
       </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>0 03/05/2018</t>
-        </is>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="36">
@@ -2910,7 +2619,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Sigil Softworks</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2918,41 +2627,34 @@
           <t>Sigil Softworks</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Sigil Softworks</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Multi-player, PvP, Online PvP, Co-op, Online Co-op, Steam Achievements, Full controller support, Family Sharing</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Multi-player, PvP, Online PvP, Co-op, Online Co-op, Steam Achievements, Full controller support, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
           <t>Action, Indie</t>
         </is>
       </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>1 To be announced</t>
-        </is>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -2973,52 +2675,43 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>English, Russian</t>
+          <t>TheDreik Xeneder</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TheDreik Xeneder</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
           <t>Phoenix Reborn Games</t>
         </is>
       </c>
+      <c r="G37" t="n">
+        <v>449</v>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>PLN 449 449</t>
+          <t>Single-player, Steam Achievements, Full controller support, Family Sharing</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Single-player, Steam Achievements, Full controller support, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
           <t>Action, Indie</t>
         </is>
       </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>0 26/01/2018</t>
-        </is>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="38">
@@ -3040,7 +2733,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">English   , French   , Italian   , German   , Spanish - Spain   , Arabic   , Bulgarian   , Portuguese - Brazil   , Hungarian   , Greek   , Danish   , Traditional Chinese   , Simplified Chinese   , Korean   , Dutch   , Norwegian   , Polish   , Portuguese - Portugal   , Romanian   , Russian   , Thai   , Turkish   , Ukrainian   , Finnish   , Czech   , Swedish   , Japanese   , Vietnamese   , Spanish - Latin America        </t>
+          <t>Crew Lab</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3048,44 +2741,35 @@
           <t>Crew Lab</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Crew Lab</t>
-        </is>
+      <c r="G38" t="n">
+        <v>449</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>PLN 449 449</t>
+          <t>Single-player, Steam Achievements, Family Sharing</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Single-player, Steam Achievements, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
           <t>Casual, Indie</t>
         </is>
       </c>
-      <c r="K38" t="n">
+      <c r="J38" t="n">
+        <v>325</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
         <v>1</v>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>0 17/06/2018</t>
-        </is>
-      </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>1800</v>
       </c>
       <c r="N38" t="n">
-        <v>325</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="39">
@@ -3107,7 +2791,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">English   , French   , Italian   , German   , Spanish - Spain   , Arabic   , Bulgarian   , Portuguese - Brazil   , Hungarian   , Greek   , Danish   , Traditional Chinese   , Simplified Chinese   , Korean   , Dutch   , Norwegian   , Polish   , Portuguese - Portugal   , Romanian   , Russian   , Thai   , Turkish   , Ukrainian   , Finnish   , Czech   , Swedish   , Japanese   , Vietnamese   , Spanish - Latin America        </t>
+          <t>Crew Lab</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3115,44 +2799,35 @@
           <t>Crew Lab</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Crew Lab</t>
-        </is>
+      <c r="G39" t="n">
+        <v>449</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>PLN 449 449</t>
+          <t>Single-player, Steam Achievements, Family Sharing</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Single-player, Steam Achievements, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
           <t>Casual, Indie</t>
         </is>
       </c>
-      <c r="K39" t="n">
+      <c r="J39" t="n">
+        <v>220</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
         <v>1</v>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>0 31/05/2018</t>
-        </is>
-      </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>2230</v>
       </c>
       <c r="N39" t="n">
-        <v>220</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="40">
@@ -3174,7 +2849,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>90E GAMES</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3182,44 +2857,35 @@
           <t>90E GAMES</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>90E GAMES</t>
-        </is>
+      <c r="G40" t="n">
+        <v>449</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>PLN 449 449</t>
+          <t>Single-player, Family Sharing</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Single-player, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
           <t>Action, Adventure, Casual, Indie, Simulation</t>
         </is>
       </c>
-      <c r="K40" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>0 31/01/2018</t>
-        </is>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="41">
@@ -3241,7 +2907,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">English   , German, Spanish - Spain, Spanish - Latin America, Portuguese - Brazil, Portuguese - Portugal, Polish     </t>
+          <t>Crystal Shard</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3249,44 +2915,35 @@
           <t>Crystal Shard</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Crystal Shard</t>
-        </is>
+      <c r="G41" t="n">
+        <v>4599</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>PLN 4599 4599</t>
+          <t>Single-player, Steam Achievements, Full controller support, Steam Workshop, Camera Comfort, Color Alternatives, Custom Volume Controls, Adjustable Difficulty, Keyboard Only Option, Playable without Timed Input, Subtitle Options, Steam Cloud, Steam Leaderboards, Includes level editor, Family Sharing</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Single-player, Steam Achievements, Full controller support, Steam Workshop, Camera Comfort, Color Alternatives, Custom Volume Controls, Adjustable Difficulty, Keyboard Only Option, Playable without Timed Input, Subtitle Options, Steam Cloud, Steam Leaderboards, Includes level editor, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
           <t>Action, Indie</t>
         </is>
       </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>0 08/12/2019</t>
-        </is>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+        <v>2019</v>
       </c>
     </row>
     <row r="42">
@@ -3308,7 +2965,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">English        </t>
+          <t>Renegade Games</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3316,44 +2973,35 @@
           <t>Renegade Games</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Renegade Games</t>
-        </is>
+      <c r="G42" t="n">
+        <v>497</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>PLN 497 497</t>
+          <t>Single-player, Family Sharing</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Single-player, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
           <t>Action, Adventure, Casual, Indie</t>
         </is>
       </c>
-      <c r="K42" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>0 28/01/2018</t>
-        </is>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
       </c>
     </row>
     <row r="43">
@@ -3379,52 +3027,111 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">English        </t>
+          <t>Primitive Studio</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Primitive Studio</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
           <t>Conglomerate 5</t>
         </is>
       </c>
+      <c r="G43" t="n">
+        <v>449</v>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>PLN 449 449</t>
+          <t>Single-player, Family Sharing</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Single-player, Family Sharing</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
           <t>Action, Adventure, Indie, Strategy</t>
         </is>
       </c>
-      <c r="K43" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>0 01/02/2018</t>
-        </is>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ball of Wonder</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Clowns are freak you out? It's time to revenge! + Ball of Wonder is an arkanoid style game, in the magnicifent world of circuses. Play througth 50 levels in 9 game mode alone or in cooperate with your friend. Destroy the puzzle elements, Ferris wheel' steats and clowns. + Ball of Wonder has 9 different power-ups and you need to activate them manualy. If you have some power-up at the and of the level, you will got them in the next one. + Remember, there is 9 different game mode in Ball of Wonder, like: + -Destroy everything + -Gather points + -Pop up the balloons + -Destroy everything in the dark + -etc +  + Oh, and before i forgot: there's two boss fight too...one of them is againts a big, bad clown. Go and catch it!</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>White Rabbit Games</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>My Way Games</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>4599</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Single-player, Multi-player, Co-op, Shared/Split Screen Co-op, Shared/Split Screen, Steam Achievements, Steam Trading Cards, Partial Controller Support, Remote Play Together, Family Sharing</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Casual, Indie</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>36</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2016</v>
       </c>
     </row>
   </sheetData>
